--- a/influencer_forms/046_social_media_influencer_collaboration_request_form--influencer_forms.xlsx
+++ b/influencer_forms/046_social_media_influencer_collaboration_request_form--influencer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -788,8 +788,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -817,12 +817,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'image'}</t>
+          <t>image</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Image'}</t>
+          <t>Image</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'video'}</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Video'}</t>
+          <t>Video</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'audio'}</t>
+          <t>audio</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Audio'}</t>
+          <t>Audio</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'text'}</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Text'}</t>
+          <t>Text</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'fashion'}</t>
+          <t>fashion</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Fashion'}</t>
+          <t>Fashion</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'beauty'}</t>
+          <t>beauty</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Beauty'}</t>
+          <t>Beauty</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'food'}</t>
+          <t>food</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Food'}</t>
+          <t>Food</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'sports'}</t>
+          <t>sports</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Sports'}</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'gaming'}</t>
+          <t>gaming</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Gaming'}</t>
+          <t>Gaming</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'travel'}</t>
+          <t>travel</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Travel'}</t>
+          <t>Travel</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'in-app'}</t>
+          <t>in-app</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'In-app'}</t>
+          <t>In-app</t>
         </is>
       </c>
     </row>
